--- a/excel/modele_arbitrage.xlsx
+++ b/excel/modele_arbitrage.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32</v>
+        <v>79.45500183105469</v>
       </c>
     </row>
     <row r="18">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1.08</v>
+        <v>1.154467821121216</v>
       </c>
     </row>
     <row r="19">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3.2</v>
+        <v>2.911999940872192</v>
       </c>
     </row>
     <row r="20">

--- a/excel/modele_arbitrage.xlsx
+++ b/excel/modele_arbitrage.xlsx
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.911999940872192</v>
+        <v>2.910000085830688</v>
       </c>
     </row>
     <row r="20">
